--- a/results/human_health_breakdown/2050/propanol production, DAC carbon dioxide, wind hydrogen, green ethylene.xlsx
+++ b/results/human_health_breakdown/2050/propanol production, DAC carbon dioxide, wind hydrogen, green ethylene.xlsx
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>3.534307678861598E-06</v>
+        <v>3.320911490147908E-06</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>1.11633999743765E-07</v>
+        <v>1.116339997437652E-07</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -475,7 +475,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>5.634371728002278E-07</v>
+        <v>5.634371728002284E-07</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -492,7 +492,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>1.810452576646581E-06</v>
+        <v>1.810452576646583E-06</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>2.622544745460295E-07</v>
+        <v>5.03858097060219E-08</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>8.173655151160663E-10</v>
+        <v>3.49348579711216E-11</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>1.00490634189377E-09</v>
+        <v>2.598101166689868E-10</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -560,7 +560,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>1.60214921185099E-08</v>
+        <v>1.602149211850994E-08</v>
       </c>
       <c r="E9">
         <v>1</v>
